--- a/public/samples/commissions_template.xlsx
+++ b/public/samples/commissions_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NextSAAS\agencies\public\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED7A8C6-9890-41AA-B0C3-66F3657463FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B833675A-5427-4902-A152-39CB1F4E56E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t>University Name*</t>
   </si>
@@ -50,27 +50,6 @@
     <t>Status</t>
   </si>
   <si>
-    <t xml:space="preserve"> The University Of Oklahoma</t>
-  </si>
-  <si>
-    <t>Bachelors</t>
-  </si>
-  <si>
-    <t>percentage</t>
-  </si>
-  <si>
-    <t>New Entry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aberystwyth University </t>
-  </si>
-  <si>
-    <t>Masters</t>
-  </si>
-  <si>
-    <t>fixed</t>
-  </si>
-  <si>
     <t>Field</t>
   </si>
   <si>
@@ -135,6 +114,27 @@
   </si>
   <si>
     <t>Auto-calculated field - Do not modify</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>university</t>
+  </si>
+  <si>
+    <t>study_level</t>
+  </si>
+  <si>
+    <t>commission_value</t>
+  </si>
+  <si>
+    <t>commission_type</t>
+  </si>
+  <si>
+    <t>no_of_installments</t>
+  </si>
+  <si>
+    <t>remark</t>
   </si>
 </sst>
 </file>
@@ -519,7 +519,7 @@
     <col min="3" max="3" width="28.3984375" customWidth="1"/>
     <col min="4" max="4" width="25.796875" customWidth="1"/>
     <col min="5" max="5" width="22.59765625" customWidth="1"/>
-    <col min="6" max="6" width="12.796875" customWidth="1"/>
+    <col min="6" max="6" width="19.69921875" customWidth="1"/>
     <col min="7" max="7" width="18.796875" customWidth="1"/>
     <col min="9" max="9" width="20.19921875" customWidth="1"/>
     <col min="10" max="10" width="15.796875" customWidth="1"/>
@@ -531,67 +531,29 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3">
-        <v>2000</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-    </row>
+    <row r="2" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:7" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -2611,35 +2573,35 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2647,21 +2609,21 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2669,10 +2631,10 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2680,10 +2642,10 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2691,21 +2653,21 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2713,10 +2675,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2724,10 +2686,10 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2735,10 +2697,10 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2746,10 +2708,10 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2757,10 +2719,10 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
